--- a/public/更新賃料検討_入力シート.xlsx
+++ b/public/更新賃料検討_入力シート.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,13 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -534,7 +540,37 @@
           <t>所在階</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>間取り</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>契約用途</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>改装時期</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>改装内容</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>家具の有無</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>前回更新日</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>更新を検討している部屋。1行だけ記入する。</t>
         </is>
@@ -581,44 +617,81 @@
       <c r="J2" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>1LDK</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>居住用（事務所使用可）</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>洗面台・浴室・フローリング交換</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="L3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="L4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>・現在家賃: 税込・月額。管理費は含めない</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="L5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>・現在管理費: 税込・月額。無ければ0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="L6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>・面積(㎡): 専有・契約・壁芯の別は区別しない</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="L7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>・築年月: YYYY-MM または YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>・前回更新日: 「前回から◯年据え置き」を説明に使う</t>
         </is>
       </c>
     </row>
@@ -633,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -646,7 +719,12 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -700,9 +778,34 @@
           <t>所在階</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>周辺の募集図面から転記する。査定賃料の自動算出には5件以上が必要。ここに入れた行はすべて集計対象になるので、条件の合わない物件は入れないこと。</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>募集元  ●</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>確認日  ●</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>出典</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>本住戸との共通点</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>賃料差の要因</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>周辺の募集図面から転記する。査定賃料の自動算出には5件以上が必要。ここに入れた行はすべて集計対象になるので、条件の合わない物件は入れないこと。算定に使った事例はすべて借主向け資料に掲載されるため、募集元と確認日は必須。</t>
         </is>
       </c>
     </row>
@@ -747,30 +850,69 @@
       <c r="J2" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>株式会社モリモトクオリティ</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>募集図面 p.2 / https://…</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>同一駅徒歩3分圏・1LDK・40㎡前後</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>築6年新しく、オートロック・宅配ボックスあり</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>● の付いた列は必須です。2行目は記入例なので消してから使ってください。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="L3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>金額はすべて税込。家賃と管理費は分けて入れ、アプリが合算した月額総額で計算する。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="L4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>・賃料: 税込・月額。管理費は含めない</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="L5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>・管理費: 共益費を含む。無ければ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>・募集元: 借主が自分で確認できるようにするため必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>・確認日: 募集条件を確認した日。必須</t>
         </is>
       </c>
     </row>
